--- a/artfynd/A 781-2023 artfynd.xlsx
+++ b/artfynd/A 781-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 781-2023 artfynd.xlsx
+++ b/artfynd/A 781-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 781-2023 artfynd.xlsx
+++ b/artfynd/A 781-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105903703</v>
+        <v>111817582</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +717,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 781, Ankarsrums säteri, Sm</t>
+          <t>A 718 m fl, Sälden, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578561.4777754117</v>
+        <v>578499</v>
       </c>
       <c r="R2" t="n">
-        <v>6398676.640961859</v>
+        <v>6398731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105903668</v>
+        <v>119300328</v>
       </c>
       <c r="B3" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,45 +795,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>655</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 781, Ankarsrums säteri, Sm</t>
+          <t>A 781, Sälden, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578403.3593176366</v>
+        <v>578526</v>
       </c>
       <c r="R3" t="n">
-        <v>6398743.544336931</v>
+        <v>6398588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,29 +860,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -916,60 +886,63 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Susanne Hernqvist, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105903706</v>
+        <v>119300340</v>
       </c>
       <c r="B4" t="n">
-        <v>79764</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3929</v>
+        <v>655</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 781, Ankarsrums säteri, Sm</t>
+          <t>A 781, Sälden, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578561.4777754117</v>
+        <v>578394</v>
       </c>
       <c r="R4" t="n">
-        <v>6398676.640961859</v>
+        <v>6398753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,22 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,49 +995,44 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Susanne Hernqvist, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111817582</v>
+        <v>111817611</v>
       </c>
       <c r="B5" t="n">
-        <v>88283</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>655</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578499</v>
+        <v>578480</v>
       </c>
       <c r="R5" t="n">
-        <v>6398731</v>
+        <v>6398699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Relativt tunn asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,15 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111817611</v>
+        <v>105903703</v>
       </c>
       <c r="B6" t="n">
-        <v>89416</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1200,14 +1158,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 718 m fl, Sälden, Ankarsrum, Sm</t>
+          <t>A 781, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578480</v>
+        <v>578561</v>
       </c>
       <c r="R6" t="n">
-        <v>6398700</v>
+        <v>6398677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,17 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Relativt tunn asp.</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,42 +1225,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111817654</v>
+        <v>119300290</v>
       </c>
       <c r="B7" t="n">
-        <v>89363</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5445</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,14 +1267,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 718 m fl, Sälden, Ankarsrum, Sm</t>
+          <t>A 781, Sälden, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578450</v>
+        <v>578582</v>
       </c>
       <c r="R7" t="n">
-        <v>6398641</v>
+        <v>6398691</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,17 +1301,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På relativt tunn ek.</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,68 +1327,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119300340</v>
+        <v>105903706</v>
       </c>
       <c r="B8" t="n">
-        <v>89441</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>655</v>
+        <v>3929</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Roth.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 781, Sälden, Sm</t>
+          <t>A 781, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578394</v>
+        <v>578561</v>
       </c>
       <c r="R8" t="n">
-        <v>6398753</v>
+        <v>6398677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,49 +1428,44 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119300290</v>
+        <v>105903668</v>
       </c>
       <c r="B9" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>5445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1552,14 +1477,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 781, Sälden, Sm</t>
+          <t>A 781, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578582</v>
+        <v>578403</v>
       </c>
       <c r="R9" t="n">
-        <v>6398691</v>
+        <v>6398744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,19 +1511,19 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1612,22 +1537,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119300309</v>
+        <v>111817654</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,26 +1574,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 781, Sälden, Sm</t>
+          <t>A 718 m fl, Sälden, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578575</v>
+        <v>578450</v>
       </c>
       <c r="R10" t="n">
-        <v>6398650</v>
+        <v>6398641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,12 +1620,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På relativt tunn ek.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,22 +1651,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119300328</v>
+        <v>119300309</v>
       </c>
       <c r="B11" t="n">
-        <v>89441</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>655</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1784,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578526</v>
+        <v>578575</v>
       </c>
       <c r="R11" t="n">
-        <v>6398588</v>
+        <v>6398650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,7 +1760,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
